--- a/output/pdf_financials_xlsx/FAIR.xlsx
+++ b/output/pdf_financials_xlsx/FAIR.xlsx
@@ -2766,13 +2766,13 @@
         <v>0.268804</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.005954</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.005954</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.533075</v>
       </c>
     </row>
     <row r="93">
@@ -4564,7 +4564,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5148,7 +5152,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -5642,7 +5650,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FAIR.xlsx
+++ b/output/pdf_financials_xlsx/FAIR.xlsx
@@ -1285,16 +1285,16 @@
         <v>0.499983</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.008421</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002034</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001312</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.745835</v>
       </c>
     </row>
     <row r="35">
@@ -1335,16 +1335,16 @@
         <v>0.499983</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.008421</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002034</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001312</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.745835</v>
       </c>
     </row>
     <row r="37">
@@ -1635,16 +1635,16 @@
         <v>0.010168</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.017524</v>
+        <v>0.009103</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.017847</v>
+        <v>0.015813</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.067703</v>
+        <v>0.06639100000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.993957</v>
+        <v>1.248122</v>
       </c>
     </row>
     <row r="49">
@@ -3544,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.059326</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.059326</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9280,7 +9280,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -10072,7 +10076,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FAIR.xlsx
+++ b/output/pdf_financials_xlsx/FAIR.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.03375</v>
+        <v>0.039741</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.06075</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.03375</v>
+        <v>0.039741</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.348959</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.03375</v>
+        <v>-0.039741</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.348959</v>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039668</v>
       </c>
     </row>
     <row r="112">
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039668</v>
       </c>
     </row>
     <row r="135">
@@ -3843,7 +3843,7 @@
         <v>-0.076921</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-4.305802</v>
+        <v>-4.34547</v>
       </c>
     </row>
   </sheetData>
@@ -7508,7 +7508,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -13308,7 +13312,11 @@
           <t>Office expense</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E206" s="5" t="n">
         <v>0.005991</v>
       </c>
